--- a/woorden.xlsx
+++ b/woorden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CE200E-08C8-4649-92C1-484E477F35E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A72D78E-5264-474C-B3B4-445C2EFF7591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4321" uniqueCount="2114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4445" uniqueCount="2174">
   <si>
     <t>de wijn</t>
   </si>
@@ -6378,13 +6378,210 @@
   </si>
   <si>
     <t>sex</t>
+  </si>
+  <si>
+    <t>Frans</t>
+  </si>
+  <si>
+    <t>à midi</t>
+  </si>
+  <si>
+    <t>Van In 5</t>
+  </si>
+  <si>
+    <t>un directeur</t>
+  </si>
+  <si>
+    <t>een directeur</t>
+  </si>
+  <si>
+    <t>une faute</t>
+  </si>
+  <si>
+    <t>een fout</t>
+  </si>
+  <si>
+    <t>écrire</t>
+  </si>
+  <si>
+    <t>commencer</t>
+  </si>
+  <si>
+    <t>op de middag</t>
+  </si>
+  <si>
+    <t>le français</t>
+  </si>
+  <si>
+    <t>het Frans</t>
+  </si>
+  <si>
+    <t>une directrice</t>
+  </si>
+  <si>
+    <t>een directrice</t>
+  </si>
+  <si>
+    <t>middag</t>
+  </si>
+  <si>
+    <t>midi</t>
+  </si>
+  <si>
+    <t>une leçon</t>
+  </si>
+  <si>
+    <t>een les</t>
+  </si>
+  <si>
+    <t>Il est quelle heure?</t>
+  </si>
+  <si>
+    <t>Hoe laat is het?</t>
+  </si>
+  <si>
+    <t>een minuut</t>
+  </si>
+  <si>
+    <t>une minute</t>
+  </si>
+  <si>
+    <t>lire</t>
+  </si>
+  <si>
+    <t>lezen</t>
+  </si>
+  <si>
+    <t>Il est une heure</t>
+  </si>
+  <si>
+    <t>Het is één uur</t>
+  </si>
+  <si>
+    <t>een woord</t>
+  </si>
+  <si>
+    <t>un mot</t>
+  </si>
+  <si>
+    <t>parler</t>
+  </si>
+  <si>
+    <t>praten</t>
+  </si>
+  <si>
+    <t>avant</t>
+  </si>
+  <si>
+    <t>voor</t>
+  </si>
+  <si>
+    <t>à six heures</t>
+  </si>
+  <si>
+    <t>om zes uur</t>
+  </si>
+  <si>
+    <t>l'après-midi</t>
+  </si>
+  <si>
+    <t>de namiddag</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>À</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> quelle heure?</t>
+    </r>
+  </si>
+  <si>
+    <t>Om hoe laat?</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>après</t>
+  </si>
+  <si>
+    <t>une journée</t>
+  </si>
+  <si>
+    <t>een dag</t>
+  </si>
+  <si>
+    <t>een uur</t>
+  </si>
+  <si>
+    <t>une heure</t>
+  </si>
+  <si>
+    <t>le néerlandais</t>
+  </si>
+  <si>
+    <t>het Nederlands</t>
+  </si>
+  <si>
+    <t>sans</t>
+  </si>
+  <si>
+    <t>une tartine</t>
+  </si>
+  <si>
+    <t>een boterham</t>
+  </si>
+  <si>
+    <t>de avond</t>
+  </si>
+  <si>
+    <t>le soir</t>
+  </si>
+  <si>
+    <t>le matin</t>
+  </si>
+  <si>
+    <t>de ochtend</t>
+  </si>
+  <si>
+    <t>een seconde</t>
+  </si>
+  <si>
+    <t>une seconde</t>
+  </si>
+  <si>
+    <t>une phrase</t>
+  </si>
+  <si>
+    <t>een zin</t>
+  </si>
+  <si>
+    <t>travailler</t>
+  </si>
+  <si>
+    <t>werken</t>
+  </si>
+  <si>
+    <t>le temps</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6405,6 +6602,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -6427,12 +6636,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -6713,7 +6923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3604FC4-2915-4560-8271-BF036F1F45A7}">
-  <dimension ref="A1:H720"/>
+  <dimension ref="A1:H751"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.6328125" bestFit="1" customWidth="1"/>
@@ -25438,8 +25648,629 @@
         <v>5</v>
       </c>
     </row>
+    <row r="721" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A721" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B721" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C721" s="2">
+        <v>1</v>
+      </c>
+      <c r="D721">
+        <v>1</v>
+      </c>
+      <c r="E721" t="s">
+        <v>2117</v>
+      </c>
+      <c r="G721" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="722" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A722" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B722" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C722" s="2">
+        <v>1</v>
+      </c>
+      <c r="D722">
+        <v>2</v>
+      </c>
+      <c r="E722" t="s">
+        <v>2119</v>
+      </c>
+      <c r="G722" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="723" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A723" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B723" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C723" s="2">
+        <v>1</v>
+      </c>
+      <c r="D723">
+        <v>3</v>
+      </c>
+      <c r="E723" t="s">
+        <v>2121</v>
+      </c>
+      <c r="G723" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="724" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A724" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B724" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C724" s="2">
+        <v>1</v>
+      </c>
+      <c r="D724">
+        <v>4</v>
+      </c>
+      <c r="E724" t="s">
+        <v>2122</v>
+      </c>
+      <c r="G724" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="725" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A725" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B725" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C725" s="2">
+        <v>1</v>
+      </c>
+      <c r="D725">
+        <v>5</v>
+      </c>
+      <c r="E725" t="s">
+        <v>2115</v>
+      </c>
+      <c r="G725" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="726" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A726" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B726" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C726" s="2">
+        <v>1</v>
+      </c>
+      <c r="D726">
+        <v>6</v>
+      </c>
+      <c r="E726" t="s">
+        <v>2124</v>
+      </c>
+      <c r="G726" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="727" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A727" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B727" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C727" s="2">
+        <v>1</v>
+      </c>
+      <c r="D727">
+        <v>7</v>
+      </c>
+      <c r="E727" t="s">
+        <v>2126</v>
+      </c>
+      <c r="G727" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="728" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A728" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B728" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C728" s="2">
+        <v>1</v>
+      </c>
+      <c r="D728">
+        <v>8</v>
+      </c>
+      <c r="E728" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G728" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="729" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A729" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B729" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C729" s="2">
+        <v>1</v>
+      </c>
+      <c r="D729">
+        <v>9</v>
+      </c>
+      <c r="E729" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G729" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="730" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A730" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B730" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C730" s="2">
+        <v>1</v>
+      </c>
+      <c r="D730">
+        <v>10</v>
+      </c>
+      <c r="E730" t="s">
+        <v>2132</v>
+      </c>
+      <c r="G730" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="731" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A731" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B731" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C731" s="2">
+        <v>1</v>
+      </c>
+      <c r="D731">
+        <v>11</v>
+      </c>
+      <c r="E731" t="s">
+        <v>2135</v>
+      </c>
+      <c r="G731" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="732" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A732" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B732" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C732" s="2">
+        <v>1</v>
+      </c>
+      <c r="D732">
+        <v>12</v>
+      </c>
+      <c r="E732" t="s">
+        <v>2136</v>
+      </c>
+      <c r="G732" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="733" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A733" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B733" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C733" s="2">
+        <v>1</v>
+      </c>
+      <c r="D733">
+        <v>13</v>
+      </c>
+      <c r="E733" t="s">
+        <v>2138</v>
+      </c>
+      <c r="G733" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="734" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A734" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B734" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C734" s="2">
+        <v>1</v>
+      </c>
+      <c r="D734">
+        <v>14</v>
+      </c>
+      <c r="E734" t="s">
+        <v>2141</v>
+      </c>
+      <c r="G734" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="735" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A735" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B735" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C735" s="2">
+        <v>1</v>
+      </c>
+      <c r="D735">
+        <v>15</v>
+      </c>
+      <c r="E735" t="s">
+        <v>2142</v>
+      </c>
+      <c r="G735" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="736" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A736" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B736" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C736" s="2">
+        <v>1</v>
+      </c>
+      <c r="D736">
+        <v>16</v>
+      </c>
+      <c r="E736" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G736" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="737" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A737" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B737" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C737" s="2">
+        <v>1</v>
+      </c>
+      <c r="D737">
+        <v>17</v>
+      </c>
+      <c r="E737" t="s">
+        <v>2146</v>
+      </c>
+      <c r="G737" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="738" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A738" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B738" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C738" s="2">
+        <v>1</v>
+      </c>
+      <c r="D738">
+        <v>18</v>
+      </c>
+      <c r="E738" t="s">
+        <v>2148</v>
+      </c>
+      <c r="G738" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="739" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A739" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B739" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C739" s="2">
+        <v>1</v>
+      </c>
+      <c r="D739">
+        <v>19</v>
+      </c>
+      <c r="E739" s="3" t="s">
+        <v>2150</v>
+      </c>
+      <c r="G739" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="740" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A740" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B740" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C740" s="2">
+        <v>1</v>
+      </c>
+      <c r="D740">
+        <v>20</v>
+      </c>
+      <c r="E740" s="3" t="s">
+        <v>2153</v>
+      </c>
+      <c r="G740" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="741" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A741" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B741" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C741" s="2">
+        <v>1</v>
+      </c>
+      <c r="D741">
+        <v>21</v>
+      </c>
+      <c r="E741" s="3" t="s">
+        <v>2154</v>
+      </c>
+      <c r="G741" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="742" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A742" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B742" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C742" s="2">
+        <v>1</v>
+      </c>
+      <c r="D742">
+        <v>22</v>
+      </c>
+      <c r="E742" s="3" t="s">
+        <v>2157</v>
+      </c>
+      <c r="G742" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="743" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A743" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B743" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C743" s="2">
+        <v>1</v>
+      </c>
+      <c r="D743">
+        <v>23</v>
+      </c>
+      <c r="E743" s="3" t="s">
+        <v>2158</v>
+      </c>
+      <c r="G743" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="744" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A744" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B744" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C744" s="2">
+        <v>1</v>
+      </c>
+      <c r="D744">
+        <v>24</v>
+      </c>
+      <c r="E744" s="3" t="s">
+        <v>2160</v>
+      </c>
+      <c r="G744" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="745" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A745" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B745" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C745" s="2">
+        <v>1</v>
+      </c>
+      <c r="D745">
+        <v>25</v>
+      </c>
+      <c r="E745" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="G745" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="746" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A746" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B746" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C746" s="2">
+        <v>1</v>
+      </c>
+      <c r="D746">
+        <v>26</v>
+      </c>
+      <c r="E746" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="G746" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="747" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A747" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B747" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C747" s="2">
+        <v>1</v>
+      </c>
+      <c r="D747">
+        <v>27</v>
+      </c>
+      <c r="E747" s="3" t="s">
+        <v>2165</v>
+      </c>
+      <c r="G747" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="748" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A748" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B748" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C748" s="2">
+        <v>1</v>
+      </c>
+      <c r="D748">
+        <v>28</v>
+      </c>
+      <c r="E748" s="3" t="s">
+        <v>2168</v>
+      </c>
+      <c r="G748" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="749" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A749" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B749" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C749" s="2">
+        <v>1</v>
+      </c>
+      <c r="D749">
+        <v>29</v>
+      </c>
+      <c r="E749" s="3" t="s">
+        <v>2169</v>
+      </c>
+      <c r="G749" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="750" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A750" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B750" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C750" s="2">
+        <v>1</v>
+      </c>
+      <c r="D750">
+        <v>30</v>
+      </c>
+      <c r="E750" s="3" t="s">
+        <v>2171</v>
+      </c>
+      <c r="G750" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="751" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A751" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B751" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C751" s="2">
+        <v>1</v>
+      </c>
+      <c r="D751">
+        <v>31</v>
+      </c>
+      <c r="E751" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G751" t="s">
+        <v>2070</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/woorden.xlsx
+++ b/woorden.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A72D78E-5264-474C-B3B4-445C2EFF7591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2398A1-2441-4390-BD62-3664C65B7B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30010" yWindow="4850" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Woorden" sheetId="19" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4445" uniqueCount="2174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4445" uniqueCount="2175">
   <si>
     <t>de wijn</t>
   </si>
@@ -6384,9 +6384,6 @@
   </si>
   <si>
     <t>à midi</t>
-  </si>
-  <si>
-    <t>Van In 5</t>
   </si>
   <si>
     <t>un directeur</t>
@@ -6575,6 +6572,12 @@
   </si>
   <si>
     <t>le temps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van In Zouff 5 </t>
+  </si>
+  <si>
+    <t>Van In Zouff 5</t>
   </si>
 </sst>
 </file>
@@ -25653,19 +25656,19 @@
         <v>2114</v>
       </c>
       <c r="B721" t="s">
-        <v>2116</v>
+        <v>2173</v>
       </c>
       <c r="C721" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D721">
         <v>1</v>
       </c>
       <c r="E721" t="s">
+        <v>2116</v>
+      </c>
+      <c r="G721" t="s">
         <v>2117</v>
-      </c>
-      <c r="G721" t="s">
-        <v>2118</v>
       </c>
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.35">
@@ -25673,19 +25676,19 @@
         <v>2114</v>
       </c>
       <c r="B722" t="s">
-        <v>2116</v>
+        <v>2173</v>
       </c>
       <c r="C722" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D722">
         <v>2</v>
       </c>
       <c r="E722" t="s">
+        <v>2118</v>
+      </c>
+      <c r="G722" t="s">
         <v>2119</v>
-      </c>
-      <c r="G722" t="s">
-        <v>2120</v>
       </c>
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.35">
@@ -25693,16 +25696,16 @@
         <v>2114</v>
       </c>
       <c r="B723" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C723" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D723">
         <v>3</v>
       </c>
       <c r="E723" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="G723" t="s">
         <v>1810</v>
@@ -25713,16 +25716,16 @@
         <v>2114</v>
       </c>
       <c r="B724" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C724" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D724">
         <v>4</v>
       </c>
       <c r="E724" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="G724" t="s">
         <v>764</v>
@@ -25733,10 +25736,10 @@
         <v>2114</v>
       </c>
       <c r="B725" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C725" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D725">
         <v>5</v>
@@ -25745,7 +25748,7 @@
         <v>2115</v>
       </c>
       <c r="G725" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.35">
@@ -25753,19 +25756,19 @@
         <v>2114</v>
       </c>
       <c r="B726" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C726" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D726">
         <v>6</v>
       </c>
       <c r="E726" t="s">
+        <v>2123</v>
+      </c>
+      <c r="G726" t="s">
         <v>2124</v>
-      </c>
-      <c r="G726" t="s">
-        <v>2125</v>
       </c>
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.35">
@@ -25773,19 +25776,19 @@
         <v>2114</v>
       </c>
       <c r="B727" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C727" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D727">
         <v>7</v>
       </c>
       <c r="E727" t="s">
+        <v>2125</v>
+      </c>
+      <c r="G727" t="s">
         <v>2126</v>
-      </c>
-      <c r="G727" t="s">
-        <v>2127</v>
       </c>
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.35">
@@ -25793,19 +25796,19 @@
         <v>2114</v>
       </c>
       <c r="B728" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C728" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D728">
         <v>8</v>
       </c>
       <c r="E728" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="G728" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.35">
@@ -25813,19 +25816,19 @@
         <v>2114</v>
       </c>
       <c r="B729" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C729" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D729">
         <v>9</v>
       </c>
       <c r="E729" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G729" t="s">
         <v>2130</v>
-      </c>
-      <c r="G729" t="s">
-        <v>2131</v>
       </c>
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.35">
@@ -25833,19 +25836,19 @@
         <v>2114</v>
       </c>
       <c r="B730" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C730" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D730">
         <v>10</v>
       </c>
       <c r="E730" t="s">
+        <v>2131</v>
+      </c>
+      <c r="G730" t="s">
         <v>2132</v>
-      </c>
-      <c r="G730" t="s">
-        <v>2133</v>
       </c>
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.35">
@@ -25853,19 +25856,19 @@
         <v>2114</v>
       </c>
       <c r="B731" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C731" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D731">
         <v>11</v>
       </c>
       <c r="E731" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="G731" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.35">
@@ -25873,19 +25876,19 @@
         <v>2114</v>
       </c>
       <c r="B732" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C732" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D732">
         <v>12</v>
       </c>
       <c r="E732" t="s">
+        <v>2135</v>
+      </c>
+      <c r="G732" t="s">
         <v>2136</v>
-      </c>
-      <c r="G732" t="s">
-        <v>2137</v>
       </c>
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.35">
@@ -25893,19 +25896,19 @@
         <v>2114</v>
       </c>
       <c r="B733" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C733" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D733">
         <v>13</v>
       </c>
       <c r="E733" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G733" t="s">
         <v>2138</v>
-      </c>
-      <c r="G733" t="s">
-        <v>2139</v>
       </c>
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.35">
@@ -25913,19 +25916,19 @@
         <v>2114</v>
       </c>
       <c r="B734" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C734" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D734">
         <v>14</v>
       </c>
       <c r="E734" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="G734" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.35">
@@ -25933,19 +25936,19 @@
         <v>2114</v>
       </c>
       <c r="B735" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C735" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D735">
         <v>15</v>
       </c>
       <c r="E735" t="s">
+        <v>2141</v>
+      </c>
+      <c r="G735" t="s">
         <v>2142</v>
-      </c>
-      <c r="G735" t="s">
-        <v>2143</v>
       </c>
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.35">
@@ -25953,19 +25956,19 @@
         <v>2114</v>
       </c>
       <c r="B736" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C736" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D736">
         <v>16</v>
       </c>
       <c r="E736" t="s">
+        <v>2143</v>
+      </c>
+      <c r="G736" t="s">
         <v>2144</v>
-      </c>
-      <c r="G736" t="s">
-        <v>2145</v>
       </c>
     </row>
     <row r="737" spans="1:7" x14ac:dyDescent="0.35">
@@ -25973,19 +25976,19 @@
         <v>2114</v>
       </c>
       <c r="B737" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C737" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D737">
         <v>17</v>
       </c>
       <c r="E737" t="s">
+        <v>2145</v>
+      </c>
+      <c r="G737" t="s">
         <v>2146</v>
-      </c>
-      <c r="G737" t="s">
-        <v>2147</v>
       </c>
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.35">
@@ -25993,19 +25996,19 @@
         <v>2114</v>
       </c>
       <c r="B738" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C738" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D738">
         <v>18</v>
       </c>
       <c r="E738" t="s">
+        <v>2147</v>
+      </c>
+      <c r="G738" t="s">
         <v>2148</v>
-      </c>
-      <c r="G738" t="s">
-        <v>2149</v>
       </c>
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.35">
@@ -26013,19 +26016,19 @@
         <v>2114</v>
       </c>
       <c r="B739" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C739" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D739">
         <v>19</v>
       </c>
       <c r="E739" s="3" t="s">
+        <v>2149</v>
+      </c>
+      <c r="G739" t="s">
         <v>2150</v>
-      </c>
-      <c r="G739" t="s">
-        <v>2151</v>
       </c>
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.35">
@@ -26033,19 +26036,19 @@
         <v>2114</v>
       </c>
       <c r="B740" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C740" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D740">
         <v>20</v>
       </c>
       <c r="E740" s="3" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="G740" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="741" spans="1:7" x14ac:dyDescent="0.35">
@@ -26053,19 +26056,19 @@
         <v>2114</v>
       </c>
       <c r="B741" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C741" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D741">
         <v>21</v>
       </c>
       <c r="E741" s="3" t="s">
+        <v>2153</v>
+      </c>
+      <c r="G741" t="s">
         <v>2154</v>
-      </c>
-      <c r="G741" t="s">
-        <v>2155</v>
       </c>
     </row>
     <row r="742" spans="1:7" x14ac:dyDescent="0.35">
@@ -26073,19 +26076,19 @@
         <v>2114</v>
       </c>
       <c r="B742" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C742" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D742">
         <v>22</v>
       </c>
       <c r="E742" s="3" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="G742" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.35">
@@ -26093,19 +26096,19 @@
         <v>2114</v>
       </c>
       <c r="B743" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C743" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D743">
         <v>23</v>
       </c>
       <c r="E743" s="3" t="s">
+        <v>2157</v>
+      </c>
+      <c r="G743" t="s">
         <v>2158</v>
-      </c>
-      <c r="G743" t="s">
-        <v>2159</v>
       </c>
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.35">
@@ -26113,16 +26116,16 @@
         <v>2114</v>
       </c>
       <c r="B744" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C744" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D744">
         <v>24</v>
       </c>
       <c r="E744" s="3" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="G744" t="s">
         <v>1373</v>
@@ -26133,19 +26136,19 @@
         <v>2114</v>
       </c>
       <c r="B745" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C745" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D745">
         <v>25</v>
       </c>
       <c r="E745" s="3" t="s">
+        <v>2160</v>
+      </c>
+      <c r="G745" t="s">
         <v>2161</v>
-      </c>
-      <c r="G745" t="s">
-        <v>2162</v>
       </c>
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.35">
@@ -26153,19 +26156,19 @@
         <v>2114</v>
       </c>
       <c r="B746" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C746" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D746">
         <v>26</v>
       </c>
       <c r="E746" s="3" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="G746" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="747" spans="1:7" x14ac:dyDescent="0.35">
@@ -26173,19 +26176,19 @@
         <v>2114</v>
       </c>
       <c r="B747" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C747" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D747">
         <v>27</v>
       </c>
       <c r="E747" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="G747" t="s">
         <v>2165</v>
-      </c>
-      <c r="G747" t="s">
-        <v>2166</v>
       </c>
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.35">
@@ -26193,19 +26196,19 @@
         <v>2114</v>
       </c>
       <c r="B748" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C748" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D748">
         <v>28</v>
       </c>
       <c r="E748" s="3" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="G748" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="749" spans="1:7" x14ac:dyDescent="0.35">
@@ -26213,19 +26216,19 @@
         <v>2114</v>
       </c>
       <c r="B749" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C749" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D749">
         <v>29</v>
       </c>
       <c r="E749" s="3" t="s">
+        <v>2168</v>
+      </c>
+      <c r="G749" t="s">
         <v>2169</v>
-      </c>
-      <c r="G749" t="s">
-        <v>2170</v>
       </c>
     </row>
     <row r="750" spans="1:7" x14ac:dyDescent="0.35">
@@ -26233,19 +26236,19 @@
         <v>2114</v>
       </c>
       <c r="B750" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C750" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D750">
         <v>30</v>
       </c>
       <c r="E750" s="3" t="s">
+        <v>2170</v>
+      </c>
+      <c r="G750" t="s">
         <v>2171</v>
-      </c>
-      <c r="G750" t="s">
-        <v>2172</v>
       </c>
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.35">
@@ -26253,16 +26256,16 @@
         <v>2114</v>
       </c>
       <c r="B751" t="s">
-        <v>2116</v>
+        <v>2174</v>
       </c>
       <c r="C751" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D751">
         <v>31</v>
       </c>
       <c r="E751" s="3" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="G751" t="s">
         <v>2070</v>
